--- a/thaco/design/Office-1 DATA.xlsx
+++ b/thaco/design/Office-1 DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA34A09-C298-3C4F-9533-3AA64B768F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003A7DE1-BB2C-824B-B1DB-7C6F0B38D47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39220" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="5" r:id="rId1"/>
@@ -4245,18 +4245,91 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Đối tượng Lương ngày tại các TĐTV
-Reply:
-    LT: Lương Tháng
-LN: Lương ngày
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Comment:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">    Đối tượng Lương ngày tại các TĐTV
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Reply:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">    LT: Lương Tháng
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">LN: Lương ngày
 </t>
         </r>
       </text>
@@ -5548,7 +5621,7 @@
         <v>3</v>
       </c>
       <c r="AH2" s="38">
-        <v>4400000</v>
+        <v>6200000</v>
       </c>
       <c r="AI2" s="38"/>
       <c r="AJ2" s="38"/>
@@ -5652,7 +5725,7 @@
       <c r="AF3" s="38"/>
       <c r="AG3" s="38"/>
       <c r="AH3" s="38">
-        <v>4400000</v>
+        <v>6200000</v>
       </c>
       <c r="AI3" s="38"/>
       <c r="AJ3" s="38"/>
@@ -5758,7 +5831,7 @@
       <c r="AF4" s="38"/>
       <c r="AG4" s="38"/>
       <c r="AH4" s="38">
-        <v>4400000</v>
+        <v>6200000</v>
       </c>
       <c r="AI4" s="38"/>
       <c r="AJ4" s="38"/>
@@ -5864,7 +5937,7 @@
       <c r="AF5" s="38"/>
       <c r="AG5" s="38"/>
       <c r="AH5" s="38">
-        <v>4400000</v>
+        <v>6200000</v>
       </c>
       <c r="AI5" s="38"/>
       <c r="AJ5" s="38"/>
@@ -5972,7 +6045,7 @@
       <c r="AF6" s="38"/>
       <c r="AG6" s="38"/>
       <c r="AH6" s="38">
-        <v>4400000</v>
+        <v>6200000</v>
       </c>
       <c r="AI6" s="38"/>
       <c r="AJ6" s="38"/>
@@ -6080,7 +6153,7 @@
       <c r="AF7" s="38"/>
       <c r="AG7" s="38"/>
       <c r="AH7" s="38">
-        <v>4400000</v>
+        <v>6200000</v>
       </c>
       <c r="AI7" s="38"/>
       <c r="AJ7" s="38"/>
@@ -6190,7 +6263,7 @@
       <c r="AF8" s="38"/>
       <c r="AG8" s="38"/>
       <c r="AH8" s="38">
-        <v>4400000</v>
+        <v>6200000</v>
       </c>
       <c r="AI8" s="38"/>
       <c r="AJ8" s="38"/>
@@ -6776,6 +6849,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>